--- a/utils/monday_sprint_sprint_2026-06.xlsx
+++ b/utils/monday_sprint_sprint_2026-06.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="516">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,7 +87,7 @@
     <t>07/01/2026</t>
   </si>
   <si>
-    <t>04/03/2026</t>
+    <t>27/02/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -135,7 +135,7 @@
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>26/02/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -165,6 +165,9 @@
     <t>05/09/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Setembro</t>
   </si>
   <si>
@@ -183,7 +186,7 @@
     <t>18/07/2025</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>Julho</t>
@@ -201,9 +204,6 @@
     <t>03/12/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
     <t>35904</t>
   </si>
   <si>
@@ -300,7 +300,7 @@
     <t>20/12/2025</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -324,7 +324,7 @@
     <t>25/11/2025</t>
   </si>
   <si>
-    <t>10/03/2026</t>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>35737</t>
@@ -342,7 +342,7 @@
     <t>16/12/2025</t>
   </si>
   <si>
-    <t>01/03/2026</t>
+    <t>24/02/2026</t>
   </si>
   <si>
     <t>32839</t>
@@ -375,7 +375,7 @@
     <t>23/01/2026</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>36213</t>
@@ -615,9 +615,6 @@
     <t>Gian Lucas Corrente</t>
   </si>
   <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
     <t>36196</t>
   </si>
   <si>
@@ -666,9 +663,6 @@
     <t>27/11/2025</t>
   </si>
   <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
     <t>34073</t>
   </si>
   <si>
@@ -873,9 +867,6 @@
     <t>TEMPOS PADRÕES DE ACABAMENTO</t>
   </si>
   <si>
-    <t>Bom dia, Favor correlacionar os tempos totais que estão no roteiro na coluna "Tempo Planejado" com os dados da planilha anexa, realizar a divisão no sistema que controla os tempos das atividades complementares. A planilha anexa separa os tempos por liga, favor verificarem se é possível criar essa re</t>
-  </si>
-  <si>
     <t>36029</t>
   </si>
   <si>
@@ -1044,7 +1035,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>Semana 5</t>
@@ -1068,57 +1059,45 @@
     <t>35047</t>
   </si>
   <si>
+    <t>Atualização de aplicações</t>
+  </si>
+  <si>
+    <t>36049</t>
+  </si>
+  <si>
+    <t>FLUXO ACVO - SEGURANÇA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar nova regra na tela de abertura de ACVO [WACVO0100] incluindo duas perguntas: 1. O item possui peso de bruto maior ou igual a 10 toneladas? 2. O item possui peso de conjunto maior ou igual a 20 toneladas? Se uma delas for selecionada como "SIM", deverá abrir o setor 566 "SEGURANÇ</t>
+  </si>
+  <si>
+    <t>35081</t>
+  </si>
+  <si>
+    <t>SUGESTÃO PARA MELHORIA NA H5000</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
+  </si>
+  <si>
+    <t>Wangadner Maycoll do Nascimento Costa</t>
+  </si>
+  <si>
+    <t>Em Análise</t>
+  </si>
+  <si>
+    <t>34347</t>
+  </si>
+  <si>
+    <t>Atualizar os Pesos 2019, 2020 e 2021 Produção das Linhas</t>
+  </si>
+  <si>
+    <t>34326</t>
+  </si>
+  <si>
     <t>Dúvida</t>
   </si>
   <si>
-    <t>Atualização de aplicações</t>
-  </si>
-  <si>
-    <t>Bom dia, Preciso que as seguintes aplicações sejam atualizadas diariamente às 09h00 da manhã e às 13h00 da tarde. Estão no fluxo de suprimentos. Att</t>
-  </si>
-  <si>
-    <t>Alan Jonis da Silva</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>36049</t>
-  </si>
-  <si>
-    <t>FLUXO ACVO - SEGURANÇA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar nova regra na tela de abertura de ACVO [WACVO0100] incluindo duas perguntas: 1. O item possui peso de bruto maior ou igual a 10 toneladas? 2. O item possui peso de conjunto maior ou igual a 20 toneladas? Se uma delas for selecionada como "SIM", deverá abrir o setor 566 "SEGURANÇ</t>
-  </si>
-  <si>
-    <t>35081</t>
-  </si>
-  <si>
-    <t>SUGESTÃO PARA MELHORIA NA H5000</t>
-  </si>
-  <si>
-    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
-  </si>
-  <si>
-    <t>Wangadner Maycoll do Nascimento Costa</t>
-  </si>
-  <si>
-    <t>Em Análise</t>
-  </si>
-  <si>
-    <t>34347</t>
-  </si>
-  <si>
-    <t>Atualizar os Pesos 2019, 2020 e 2021 Produção das Linhas</t>
-  </si>
-  <si>
-    <t>34326</t>
-  </si>
-  <si>
     <t>módulo custos de manutenção</t>
   </si>
   <si>
@@ -1353,7 +1332,7 @@
     <t>27/01/2026</t>
   </si>
   <si>
-    <t>24/02/2026</t>
+    <t>19/02/2026</t>
   </si>
   <si>
     <t>31398</t>
@@ -1383,7 +1362,7 @@
     <t>08/09/2025</t>
   </si>
   <si>
-    <t>01/04/2026</t>
+    <t>27/03/2026</t>
   </si>
   <si>
     <t>23773</t>
@@ -1398,7 +1377,7 @@
     <t>19/12/2023</t>
   </si>
   <si>
-    <t>27/04/2026</t>
+    <t>22/04/2026</t>
   </si>
   <si>
     <t>35378</t>
@@ -1422,9 +1401,6 @@
     <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
   </si>
   <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
     <t>11069668388</t>
   </si>
   <si>
@@ -1509,7 +1485,7 @@
     <t>Boa tarde, Tudo certo ? Favor acrescentar na unidade de medida a seguinte medida g/cm3 Para ser possível estarem apontando nessa inspeção Att.</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>Dashboard de Change Log - Governança de TI</t>
@@ -2225,7 +2201,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -2234,12 +2210,12 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -2251,25 +2227,25 @@
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -2278,12 +2254,12 @@
         <v>41</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -2295,25 +2271,25 @@
         <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -2348,7 +2324,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>48</v>
@@ -2357,7 +2333,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>66</v>
@@ -2753,7 +2729,7 @@
         <v>114</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2762,7 +2738,7 @@
         <v>71</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2929,7 +2905,7 @@
         <v>129</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>66</v>
@@ -3008,16 +2984,16 @@
         <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -3026,7 +3002,7 @@
         <v>41</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3061,7 +3037,7 @@
         <v>140</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -3114,7 +3090,7 @@
         <v>32</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3149,7 +3125,7 @@
         <v>149</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -3193,7 +3169,7 @@
         <v>89</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>66</v>
@@ -3545,7 +3521,7 @@
         <v>89</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -3589,7 +3565,7 @@
         <v>149</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -3721,7 +3697,7 @@
         <v>187</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>66</v>
@@ -3756,7 +3732,7 @@
         <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>48</v>
@@ -3765,7 +3741,7 @@
         <v>78</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>66</v>
@@ -3818,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -3853,7 +3829,7 @@
         <v>108</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>66</v>
@@ -3867,22 +3843,22 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3897,7 +3873,7 @@
         <v>89</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3911,7 +3887,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3923,10 +3899,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3938,10 +3914,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3950,27 +3926,27 @@
         <v>41</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3985,7 +3961,7 @@
         <v>78</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3999,37 +3975,37 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>66</v>
@@ -4043,7 +4019,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -4055,10 +4031,10 @@
         <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>46</v>
@@ -4087,7 +4063,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -4099,10 +4075,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -4114,7 +4090,7 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>30</v>
@@ -4126,12 +4102,12 @@
         <v>71</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -4143,10 +4119,10 @@
         <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -4175,22 +4151,22 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>46</v>
@@ -4202,7 +4178,7 @@
         <v>48</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>103</v>
@@ -4219,22 +4195,22 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -4246,7 +4222,7 @@
         <v>48</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>162</v>
@@ -4263,7 +4239,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -4275,25 +4251,25 @@
         <v>35</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -4307,7 +4283,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -4319,25 +4295,25 @@
         <v>35</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>66</v>
@@ -4351,7 +4327,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -4363,10 +4339,10 @@
         <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -4395,22 +4371,22 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -4422,13 +4398,13 @@
         <v>48</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>41</v>
@@ -4439,7 +4415,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -4451,10 +4427,10 @@
         <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -4483,22 +4459,22 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>46</v>
@@ -4527,28 +4503,28 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>48</v>
@@ -4557,7 +4533,7 @@
         <v>140</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -4571,34 +4547,34 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>120</v>
@@ -4610,12 +4586,12 @@
         <v>41</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4627,7 +4603,7 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>30</v>
@@ -4642,10 +4618,10 @@
         <v>48</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4659,37 +4635,37 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="G61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>66</v>
@@ -4703,28 +4679,28 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="G62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>48</v>
@@ -4747,7 +4723,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4759,28 +4735,28 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>41</v>
@@ -4791,7 +4767,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4803,10 +4779,10 @@
         <v>30</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>100</v>
@@ -4835,7 +4811,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4844,25 +4820,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>30</v>
@@ -4871,15 +4847,15 @@
         <v>70</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4891,10 +4867,10 @@
         <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4923,7 +4899,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4935,25 +4911,25 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4962,12 +4938,12 @@
         <v>41</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4979,16 +4955,16 @@
         <v>35</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>48</v>
@@ -5011,7 +4987,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -5023,10 +4999,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -5038,10 +5014,10 @@
         <v>48</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -5055,40 +5031,40 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>41</v>
@@ -5099,7 +5075,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -5111,10 +5087,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -5126,10 +5102,10 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -5143,34 +5119,34 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>103</v>
@@ -5187,7 +5163,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -5199,10 +5175,10 @@
         <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -5231,34 +5207,34 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>103</v>
@@ -5275,7 +5251,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -5287,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>48</v>
@@ -5319,7 +5295,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -5331,28 +5307,28 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>103</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>32</v>
@@ -5363,7 +5339,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -5375,16 +5351,16 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>48</v>
@@ -5407,7 +5383,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -5419,10 +5395,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -5434,10 +5410,10 @@
         <v>48</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -5451,7 +5427,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5463,25 +5439,25 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>70</v>
@@ -5495,7 +5471,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -5507,39 +5483,39 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5551,10 +5527,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5566,10 +5542,10 @@
         <v>48</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5578,12 +5554,12 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5592,42 +5568,42 @@
         <v>16</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>351</v>
+        <v>30</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>354</v>
+        <v>30</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>355</v>
+        <v>30</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>356</v>
+        <v>30</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>66</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -5639,10 +5615,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5654,10 +5630,10 @@
         <v>48</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5671,7 +5647,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5683,16 +5659,16 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>48</v>
@@ -5704,7 +5680,7 @@
         <v>30</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>26</v>
@@ -5715,7 +5691,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5727,10 +5703,10 @@
         <v>30</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5759,7 +5735,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5768,19 +5744,19 @@
         <v>34</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>48</v>
@@ -5789,7 +5765,7 @@
         <v>145</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5798,12 +5774,12 @@
         <v>32</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5815,10 +5791,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5830,24 +5806,24 @@
         <v>48</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5859,10 +5835,10 @@
         <v>30</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>46</v>
@@ -5891,7 +5867,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5903,25 +5879,25 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>66</v>
@@ -5935,7 +5911,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5947,25 +5923,25 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>25</v>
@@ -5979,7 +5955,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5991,25 +5967,25 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>66</v>
@@ -6018,12 +5994,12 @@
         <v>32</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -6035,10 +6011,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -6050,7 +6026,7 @@
         <v>48</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>30</v>
@@ -6062,12 +6038,12 @@
         <v>32</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -6079,16 +6055,16 @@
         <v>35</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>48</v>
@@ -6111,7 +6087,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -6123,10 +6099,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -6138,7 +6114,7 @@
         <v>48</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>103</v>
@@ -6155,7 +6131,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -6167,10 +6143,10 @@
         <v>30</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -6199,7 +6175,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -6211,10 +6187,10 @@
         <v>30</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -6243,7 +6219,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -6255,10 +6231,10 @@
         <v>30</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -6287,7 +6263,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -6299,10 +6275,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -6314,13 +6290,13 @@
         <v>48</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>41</v>
@@ -6331,7 +6307,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -6343,25 +6319,25 @@
         <v>17</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>25</v>
@@ -6375,7 +6351,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -6387,25 +6363,25 @@
         <v>17</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>70</v>
@@ -6419,7 +6395,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -6431,25 +6407,25 @@
         <v>17</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>200</v>
+        <v>103</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>66</v>
@@ -6463,7 +6439,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -6475,10 +6451,10 @@
         <v>30</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>20</v>
@@ -6507,7 +6483,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -6519,28 +6495,28 @@
         <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>41</v>
@@ -6551,22 +6527,22 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>20</v>
@@ -6607,10 +6583,10 @@
         <v>30</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>20</v>
@@ -6631,7 +6607,7 @@
         <v>25</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>30</v>
@@ -6639,7 +6615,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -6651,10 +6627,10 @@
         <v>30</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>20</v>
@@ -6683,7 +6659,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -6695,10 +6671,10 @@
         <v>17</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>46</v>
@@ -6710,7 +6686,7 @@
         <v>48</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>30</v>
@@ -6722,12 +6698,12 @@
         <v>26</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6739,10 +6715,10 @@
         <v>30</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>20</v>
@@ -6771,7 +6747,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6783,10 +6759,10 @@
         <v>17</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>20</v>
@@ -6798,10 +6774,10 @@
         <v>48</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>25</v>
@@ -6827,7 +6803,7 @@
         <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>87</v>
@@ -6859,7 +6835,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
@@ -6871,25 +6847,25 @@
         <v>17</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>25</v>
@@ -6903,7 +6879,7 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
@@ -6915,10 +6891,10 @@
         <v>17</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>20</v>
@@ -6930,24 +6906,24 @@
         <v>48</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>15</v>
@@ -6956,13 +6932,13 @@
         <v>16</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>20</v>
@@ -6974,10 +6950,10 @@
         <v>48</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>66</v>
@@ -6986,12 +6962,12 @@
         <v>71</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>15</v>
@@ -7003,25 +6979,25 @@
         <v>35</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>25</v>
@@ -7035,7 +7011,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>15</v>
@@ -7047,22 +7023,22 @@
         <v>17</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>103</v>
@@ -7079,7 +7055,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>15</v>
@@ -7091,16 +7067,16 @@
         <v>17</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>48</v>
@@ -7109,7 +7085,7 @@
         <v>119</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>66</v>
@@ -7123,7 +7099,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>15</v>
@@ -7135,10 +7111,10 @@
         <v>30</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>46</v>
@@ -7156,7 +7132,7 @@
         <v>30</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>32</v>
@@ -7167,7 +7143,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>15</v>
@@ -7179,22 +7155,22 @@
         <v>17</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>103</v>
@@ -7203,15 +7179,15 @@
         <v>66</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>15</v>
@@ -7223,10 +7199,10 @@
         <v>17</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>20</v>
@@ -7238,16 +7214,16 @@
         <v>22</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>27</v>
@@ -7255,7 +7231,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>15</v>
@@ -7267,25 +7243,25 @@
         <v>17</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>66</v>
@@ -7294,12 +7270,12 @@
         <v>32</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -7311,25 +7287,25 @@
         <v>35</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>25</v>
@@ -7343,7 +7319,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>15</v>
@@ -7355,10 +7331,10 @@
         <v>30</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>20</v>
@@ -7387,7 +7363,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>15</v>
@@ -7399,16 +7375,16 @@
         <v>17</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>48</v>
@@ -7443,10 +7419,10 @@
         <v>30</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>20</v>
@@ -7467,7 +7443,7 @@
         <v>66</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>30</v>
@@ -7475,7 +7451,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>15</v>
@@ -7487,25 +7463,25 @@
         <v>17</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>25</v>
@@ -7531,10 +7507,10 @@
         <v>30</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>20</v>
@@ -7574,23 +7550,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7598,16 +7574,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7626,7 +7602,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -7639,7 +7615,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -7647,7 +7623,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7678,12 +7654,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="B2">
         <v>125</v>
@@ -7707,25 +7683,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7742,13 +7718,13 @@
         <v>92</v>
       </c>
       <c r="G10" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7763,7 +7739,7 @@
         <v>26</v>
       </c>
       <c r="Q10">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -7780,7 +7756,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="K11">
         <v>125</v>
@@ -7795,7 +7771,7 @@
         <v>71</v>
       </c>
       <c r="Q11">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -7821,12 +7797,12 @@
         <v>41</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -7847,7 +7823,7 @@
         <v>32</v>
       </c>
       <c r="Q13">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
@@ -7858,22 +7834,22 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -7886,7 +7862,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -7894,7 +7870,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -7902,7 +7878,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -7913,7 +7889,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7921,49 +7897,49 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
@@ -7972,91 +7948,91 @@
         <v>458</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-06.xlsx
+++ b/utils/monday_sprint_sprint_2026-06.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="427">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>35908</t>
+    <t>10973910068</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>12/01/2026</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>13/01/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9889668017</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -114,13 +114,16 @@
     <t>25/08/2025</t>
   </si>
   <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Agosto</t>
   </si>
   <si>
-    <t>35797</t>
+    <t>11021328588</t>
   </si>
   <si>
     <t>Correção</t>
@@ -138,6 +141,9 @@
     <t>33956</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -171,6 +177,9 @@
     <t>32989</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
     <t>IROG Tratamento Térmico no BI</t>
   </si>
   <si>
@@ -183,7 +192,7 @@
     <t>20/03/2026</t>
   </si>
   <si>
-    <t>35570</t>
+    <t>10977103899</t>
   </si>
   <si>
     <t>sistema de apontamento eletrônico corte pó de ferro</t>
@@ -201,10 +210,7 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>31699</t>
+    <t>10977107501</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -213,10 +219,13 @@
     <t>Copiloto Gerencial IA - Liberar todos os grupos para todos os usuários</t>
   </si>
   <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>36220</t>
+    <t>11093799893</t>
   </si>
   <si>
     <t>INFORMAÇÕES SOBRE MATERIAL DO MODELO EM FTF'S DE CONJUNTO</t>
@@ -225,9 +234,15 @@
     <t>25/01/2026</t>
   </si>
   <si>
+    <t>01/02/2026</t>
+  </si>
+  <si>
     <t>35527</t>
   </si>
   <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
     <t>Orçamento 2025</t>
   </si>
   <si>
@@ -258,6 +273,9 @@
     <t>36206</t>
   </si>
   <si>
+    <t>Comercial</t>
+  </si>
+  <si>
     <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
   </si>
   <si>
@@ -288,846 +306,813 @@
     <t>Homologação</t>
   </si>
   <si>
-    <t>35409</t>
-  </si>
-  <si>
-    <t>Fundição</t>
+    <t>10977122459</t>
   </si>
   <si>
     <t>PAINEL DOS MANIPULADORES</t>
   </si>
   <si>
-    <t>Bom dia, Os operadores de manipuladores apontam porcentagens de peças executadas. Precisamos dessa informação de fácil acesso no painel de operações, igual ao dos jatos, que aparece no detalhamento do apontamento.</t>
-  </si>
-  <si>
     <t>Baixa</t>
   </si>
   <si>
+    <t>11116098082</t>
+  </si>
+  <si>
+    <t>Correção Calculo MTBF</t>
+  </si>
+  <si>
+    <t>11021370984</t>
+  </si>
+  <si>
+    <t>[NIMBI] ATUALIZAÇÃO PARA ALTERAÇÃO DE PEDIDO</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>36229</t>
+  </si>
+  <si>
+    <t>Troca de campanha forno indução</t>
+  </si>
+  <si>
+    <t>Solicito troca sistemática da troca de campanha no forno indução, Sistema semelhante ao da troca de campanha de panelas Segue local e o sistema de corridas:</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>36213</t>
+  </si>
+  <si>
+    <t>Alteração no sistema de manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>11021353520</t>
+  </si>
+  <si>
+    <t>Ordens de Compra - Benner</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>10669224256</t>
+  </si>
+  <si>
+    <t>Criação Relatório BI ProfMix</t>
+  </si>
+  <si>
+    <t>32996</t>
+  </si>
+  <si>
+    <t>Implementação do Checklist no sistema de Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
+  </si>
+  <si>
+    <t>11093873897</t>
+  </si>
+  <si>
+    <t>Carregamento dos Croquis / Anexos / Mapeamento Digital</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>11093863589</t>
+  </si>
+  <si>
+    <t>REVISÃO DE DESENHO 3D - ALERTA DE REVISÃO</t>
+  </si>
+  <si>
+    <t>36201</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
+  </si>
+  <si>
+    <t>10977239266</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – “Pré-Transferência Aciaria” (copy)</t>
+  </si>
+  <si>
+    <t>10977239635</t>
+  </si>
+  <si>
+    <t>Cálculo de carga - Sistema de corridas</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>10977231605</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
+  </si>
+  <si>
+    <t>35452</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Melhoria no fluxo de entrega de EPI</t>
+  </si>
+  <si>
+    <t>Boa tarde! Gostaríamos de solicitar uma melhoria no sistema WMS referente ao processo de entrega de EPI. Situação atual: Quando um colaborador inicia a separação de uma pré-lista de EPI, outro colaborador não consegue acessar a mesma pré-lista. Isso gera dificuldades, pois temos entregas fracionadas</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>11093881756</t>
+  </si>
+  <si>
+    <t>Controle de refratário</t>
+  </si>
+  <si>
+    <t>10974400788</t>
+  </si>
+  <si>
+    <t>Melhoria - Checklist app CIPA</t>
+  </si>
+  <si>
+    <t>11093880405</t>
+  </si>
+  <si>
+    <t>Liberação Ensaio Mecanico Automatico</t>
+  </si>
+  <si>
+    <t>36197</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Anexar Comprovante de Entrega</t>
+  </si>
+  <si>
+    <t>Bom dia Incluir no campo de upload, a opção de salvar o comprovante de entrega (pdf, imagem etc) ao recibo de embarque. Quando realizar a inclusão, ao baixar o pdf do recibo assinado, deve puxar na pagina seguinte o comprovante de entrega.</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>11093871273</t>
+  </si>
+  <si>
+    <t>Criação de sistema para sequencia</t>
+  </si>
+  <si>
+    <t>10974310991</t>
+  </si>
+  <si>
+    <t>Retrabalhos Moldagens - apontamentos - PA104/22</t>
+  </si>
+  <si>
+    <t>35792</t>
+  </si>
+  <si>
+    <t>Criação de campos no sistema de manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
+  </si>
+  <si>
+    <t>Vitor de Oliveira da Silva</t>
+  </si>
+  <si>
+    <t>35097</t>
+  </si>
+  <si>
+    <t>Mapeamento Digital</t>
+  </si>
+  <si>
+    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
+  </si>
+  <si>
+    <t>Sergio Schmidt</t>
+  </si>
+  <si>
+    <t>35520</t>
+  </si>
+  <si>
+    <t>Aplicativo Tratamento Térmico - Melhorias</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
+  </si>
+  <si>
+    <t>33965</t>
+  </si>
+  <si>
+    <t>Apontamento de moldes Carrossel - Homologação</t>
+  </si>
+  <si>
+    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>10974666894</t>
+  </si>
+  <si>
+    <t>BUG SISTEMA MAPEAMENTO DIGITAL</t>
+  </si>
+  <si>
+    <t>11093815714</t>
+  </si>
+  <si>
+    <t>Melhoria - Incluir Dt de Entrega e Referência de Atraso</t>
+  </si>
+  <si>
+    <t>02/02/2026</t>
+  </si>
+  <si>
+    <t>11021391999</t>
+  </si>
+  <si>
+    <t>Revisão ETF no Posto de Cópia</t>
+  </si>
+  <si>
+    <t>10977126963</t>
+  </si>
+  <si>
+    <t>APONTAMENTO JATO DIRIGIDO</t>
+  </si>
+  <si>
+    <t>35467</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
+  </si>
+  <si>
+    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>10977124189</t>
+  </si>
+  <si>
+    <t>Siga - Consulta Sequencia (Alt c)</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Sistema de Controle de Importação</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>11093883758</t>
+  </si>
+  <si>
+    <t>Levantamento dos Itens EDI / Mapeamento Digital</t>
+  </si>
+  <si>
+    <t>10977471112</t>
+  </si>
+  <si>
+    <t>Implementação sistema retrabalho Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>35471</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de inventário de embalagens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia! Gostaria de solicitar uma melhoria no nosso sistema de inventário de embalagens. Atualmente, ele permite apenas a contagem, sem realizar ajustes de saldo. Precisamos que, após a conclusão da contagem, seja possível finalizar o inventário com a geração automática dos ajustes necessários nos </t>
+  </si>
+  <si>
+    <t>11021481051</t>
+  </si>
+  <si>
+    <t>Erro de carregamento</t>
+  </si>
+  <si>
+    <t>11093896475</t>
+  </si>
+  <si>
+    <t>Sistema desmoldagem</t>
+  </si>
+  <si>
+    <t>10977158397</t>
+  </si>
+  <si>
+    <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM (copy)</t>
+  </si>
+  <si>
+    <t>11093820223</t>
+  </si>
+  <si>
+    <t>Alteração CPC para calculo de Reconhecimento de Receita</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>10974622890</t>
+  </si>
+  <si>
+    <t>Automação da lista de presença - Detalhar escopo</t>
+  </si>
+  <si>
+    <t>10974712197</t>
+  </si>
+  <si>
+    <t>Inclusão de filtro por item/peça no modulo de custos de manutenção</t>
+  </si>
+  <si>
+    <t>11093891325</t>
+  </si>
+  <si>
+    <t>VERIFICAÇÃO COLUNA IROG</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>11093882471</t>
+  </si>
+  <si>
+    <t>Apontamento de Panelas</t>
+  </si>
+  <si>
+    <t>36177</t>
+  </si>
+  <si>
+    <t>Melhorias apontamento eletrônico: Manipuladores</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos, o apontamento dos Manipuladores só precisa de mais duas coisas para tirar o papel de vez. Preciso que seja feito as seguintes alterações: - Inserir a porcentagem feita da peça no painel de produção; - Tornar as informações das paradas exclusivas do painel de paradas, trocar as aba</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Santos</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>11093818583</t>
+  </si>
+  <si>
+    <t>Análise</t>
+  </si>
+  <si>
+    <t>CNPJ Alfanumérico - Instrução Normativa 2.229</t>
+  </si>
+  <si>
+    <t>11093823687</t>
+  </si>
+  <si>
+    <t>Erro no cálculo: Jato Dirigido</t>
+  </si>
+  <si>
+    <t>10977467589</t>
+  </si>
+  <si>
+    <t>BI Ronda - necessidade de implementação</t>
+  </si>
+  <si>
+    <t>10977175641</t>
+  </si>
+  <si>
+    <t>TEMPOS PADRÕES DE ACABAMENTO</t>
+  </si>
+  <si>
+    <t>11093896748</t>
+  </si>
+  <si>
+    <t>ERRO: Sistema de Custeio - Fundição</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>11021478309</t>
+  </si>
+  <si>
+    <t>Aplicação de Solda</t>
+  </si>
+  <si>
+    <t>10974820938</t>
+  </si>
+  <si>
+    <t>Criar novo código de operação para o QlikSense</t>
+  </si>
+  <si>
+    <t>10974918179</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO SISTEMA MAPEAMENTO DIGITAL</t>
+  </si>
+  <si>
+    <t>11093816472</t>
+  </si>
+  <si>
+    <t>SISTREMA TRANSFERENCIA BOOKING - INVOICE</t>
+  </si>
+  <si>
+    <t>11093842121</t>
+  </si>
+  <si>
+    <t>Consulta ligas &amp; grupos de ligas</t>
+  </si>
+  <si>
+    <t>10977175465</t>
+  </si>
+  <si>
+    <t>Painel Desmoldagem USE</t>
+  </si>
+  <si>
+    <t>10977175776</t>
+  </si>
+  <si>
+    <t>Alinhamento dos cálculos de disponibilidade</t>
+  </si>
+  <si>
+    <t>11093835423</t>
+  </si>
+  <si>
+    <t>Incluir Coluna Fases no Sistema de Investimentos</t>
+  </si>
+  <si>
+    <t>35731</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>Indicadores Moldes Moldagem USE</t>
+  </si>
+  <si>
+    <t>Bom dia. Preciso criar/adaptar um aplicativo do QlikSense. Hoje há um aplicativo que mostra as movimentações por sequência de peça, porém preciso que esse indicador seja apresentado por quantidade de moldes. Para isso, há a informação do sistema da quantidade de peças por placa de moldagem, conforme</t>
+  </si>
+  <si>
+    <t>Lucas da Silva Machado</t>
+  </si>
+  <si>
+    <t>11021132258</t>
+  </si>
+  <si>
+    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>35738</t>
+  </si>
+  <si>
+    <t>Melhoria apontamento de corte de canais</t>
+  </si>
+  <si>
+    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
+  </si>
+  <si>
+    <t>11093836788</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTOS 540 E 601</t>
+  </si>
+  <si>
+    <t>35999</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Divergência no Relatório Funil Vendas 80%</t>
+  </si>
+  <si>
+    <t>Boa tarde Edson, Feliz Ano Novo!!! Conforme verificado, o processo 94/24 foi incluído no indicador de 80% em 09/01/2026, por volta das 14h30, conforme evidenciado no print abaixo. No entanto, ao gerar o relatório "Funil Vendas 80%", o processo não está sendo apresentado. Aparentemente, o relatório s</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>10985679619</t>
+  </si>
+  <si>
+    <t>Dalca e lianco - Novos Tipos no apontamento</t>
+  </si>
+  <si>
+    <t>11021192944</t>
+  </si>
+  <si>
+    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS</t>
+  </si>
+  <si>
+    <t>11021606665</t>
+  </si>
+  <si>
+    <t>Atualização de aplicações</t>
+  </si>
+  <si>
+    <t>11093897217</t>
+  </si>
+  <si>
+    <t>FLUXO ACVO - SEGURANÇA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>10977614552</t>
+  </si>
+  <si>
+    <t>SUGESTÃO PARA MELHORIA NA H5000</t>
+  </si>
+  <si>
+    <t>Em Análise</t>
+  </si>
+  <si>
+    <t>11021583235</t>
+  </si>
+  <si>
+    <t>Atualizar os Pesos 2019, 2020 e 2021 Produção das Linhas</t>
+  </si>
+  <si>
+    <t>11021527336</t>
+  </si>
+  <si>
+    <t>módulo custos de manutenção</t>
+  </si>
+  <si>
+    <t>34960</t>
+  </si>
+  <si>
+    <t>Correção | Status da Parcela de Pgto de Invoice</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
+  </si>
+  <si>
+    <t>11093897729</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Valorização de modelos</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>11093912137</t>
+  </si>
+  <si>
+    <t>Apontamentos de Horas Acabamento</t>
+  </si>
+  <si>
+    <t>11093846437</t>
+  </si>
+  <si>
+    <t>Estratificação métodos preventiva e inspeção maquinas A e B</t>
+  </si>
+  <si>
+    <t>34919</t>
+  </si>
+  <si>
+    <t>Solicitação de BI QlikSense – Indicadores de Ofertas</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de desenvolver um BI que apresente dois indicadores relacionados ao envio de ofertas: 1. % de ofertas enviadas dentro do prazo definido no momento da abertura do PO. Este será o indicador principal. 1. Prazo médio de envio das ofertas (em dias) Apenas para acompanhamento; não haver</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>11021528207</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>10977177312</t>
+  </si>
+  <si>
+    <t>Erro IROG acabamento</t>
+  </si>
+  <si>
+    <t>11093859815</t>
+  </si>
+  <si>
+    <t>Acrescentar opção de apontamento de % nas linhas UPR</t>
+  </si>
+  <si>
+    <t>10977231604</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – Gestão de Embalagens (copy)</t>
+  </si>
+  <si>
+    <t>10977176455</t>
+  </si>
+  <si>
+    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
+  </si>
+  <si>
+    <t>10977191209</t>
+  </si>
+  <si>
+    <t>[APS] - Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
+  </si>
+  <si>
+    <t>36125</t>
+  </si>
+  <si>
+    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
+  </si>
+  <si>
     <t>Douglas Garcia</t>
   </si>
   <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>35737</t>
-  </si>
-  <si>
-    <t>Correção Calculo MTBF</t>
-  </si>
-  <si>
-    <t>32839</t>
-  </si>
-  <si>
-    <t>[NIMBI] ATUALIZAÇÃO PARA ALTERAÇÃO DE PEDIDO</t>
-  </si>
-  <si>
-    <t>36229</t>
-  </si>
-  <si>
-    <t>Troca de campanha forno indução</t>
-  </si>
-  <si>
-    <t>Solicito troca sistemática da troca de campanha no forno indução, Sistema semelhante ao da troca de campanha de panelas Segue local e o sistema de corridas:</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>36213</t>
-  </si>
-  <si>
-    <t>Alteração no sistema de manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>33395</t>
-  </si>
-  <si>
-    <t>Ordens de Compra - Benner</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>34952</t>
-  </si>
-  <si>
-    <t>Criação Relatório BI ProfMix</t>
-  </si>
-  <si>
-    <t>32996</t>
-  </si>
-  <si>
-    <t>Implementação do Checklist no sistema de Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
-  </si>
-  <si>
-    <t>36080</t>
-  </si>
-  <si>
-    <t>Carregamento dos Croquis / Anexos / Mapeamento Digital</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>36095</t>
-  </si>
-  <si>
-    <t>REVISÃO DE DESENHO 3D - ALERTA DE REVISÃO</t>
-  </si>
-  <si>
-    <t>36201</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
-  </si>
-  <si>
-    <t>35333</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – “Pré-Transferência Aciaria” (copy)</t>
-  </si>
-  <si>
-    <t>33632</t>
-  </si>
-  <si>
-    <t>Cálculo de carga - Sistema de corridas</t>
-  </si>
-  <si>
-    <t>35448</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
-  </si>
-  <si>
-    <t>35452</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Melhoria no fluxo de entrega de EPI</t>
-  </si>
-  <si>
-    <t>Boa tarde! Gostaríamos de solicitar uma melhoria no sistema WMS referente ao processo de entrega de EPI. Situação atual: Quando um colaborador inicia a separação de uma pré-lista de EPI, outro colaborador não consegue acessar a mesma pré-lista. Isso gera dificuldades, pois temos entregas fracionadas</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>36059</t>
-  </si>
-  <si>
-    <t>Controle de refratário</t>
-  </si>
-  <si>
-    <t>35803</t>
-  </si>
-  <si>
-    <t>Melhoria - Checklist app CIPA</t>
-  </si>
-  <si>
-    <t>36063</t>
-  </si>
-  <si>
-    <t>Liberação Ensaio Mecanico Automatico</t>
-  </si>
-  <si>
-    <t>36197</t>
-  </si>
-  <si>
-    <t>Anexar Comprovante de Entrega</t>
-  </si>
-  <si>
-    <t>Bom dia Incluir no campo de upload, a opção de salvar o comprovante de entrega (pdf, imagem etc) ao recibo de embarque. Quando realizar a inclusão, ao baixar o pdf do recibo assinado, deve puxar na pagina seguinte o comprovante de entrega.</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>36093</t>
-  </si>
-  <si>
-    <t>Criação de sistema para sequencia</t>
-  </si>
-  <si>
-    <t>35810</t>
-  </si>
-  <si>
-    <t>Retrabalhos Moldagens - apontamentos - PA104/22</t>
-  </si>
-  <si>
-    <t>35792</t>
-  </si>
-  <si>
-    <t>Criação de campos no sistema de manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Precisamos criar alguns campos na janela de requisições do almoxarifado no sistema manutenção, a finalidade é que conseguimos ter informações precisas referentes ao material requisitado. Os campos seriam: Família/Máquina/Código/Marca. Em anexo estou enviando uma imagem de sugestão, estou a </t>
-  </si>
-  <si>
-    <t>Vitor de Oliveira da Silva</t>
-  </si>
-  <si>
-    <t>35097</t>
-  </si>
-  <si>
-    <t>Mapeamento Digital</t>
-  </si>
-  <si>
-    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
-  </si>
-  <si>
-    <t>Sergio Schmidt</t>
-  </si>
-  <si>
-    <t>35520</t>
-  </si>
-  <si>
-    <t>Aplicativo Tratamento Térmico - Melhorias</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
-  </si>
-  <si>
-    <t>33965</t>
-  </si>
-  <si>
-    <t>Apontamento de moldes Carrossel - Homologação</t>
-  </si>
-  <si>
-    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>35753</t>
-  </si>
-  <si>
-    <t>BUG SISTEMA MAPEAMENTO DIGITAL</t>
-  </si>
-  <si>
-    <t>36196</t>
-  </si>
-  <si>
-    <t>Melhoria - Incluir Dt de Entrega e Referência de Atraso</t>
-  </si>
-  <si>
-    <t>32350</t>
-  </si>
-  <si>
-    <t>Revisão ETF no Posto de Cópia</t>
-  </si>
-  <si>
-    <t>35523</t>
-  </si>
-  <si>
-    <t>APONTAMENTO JATO DIRIGIDO</t>
-  </si>
-  <si>
-    <t>35467</t>
-  </si>
-  <si>
-    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
-  </si>
-  <si>
-    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>Siga - Consulta Sequencia (Alt c)</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Sistema de Controle de Importação</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>36079</t>
-  </si>
-  <si>
-    <t>Levantamento dos Itens EDI / Mapeamento Digital</t>
-  </si>
-  <si>
-    <t>33489</t>
-  </si>
-  <si>
-    <t>Implementação sistema retrabalho Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Boa tarde! Conforme tratativas já feitas anteriores @Edson João Hammermeister, oficializo a abertura do chamado para criação da aplicação no SENSE com foco no retrabalho do Tratamento Térmico. Conforme já conversamos, o Lucas, antes de seu desligamento da Altona, já havia deixado esta aplicação prat</t>
-  </si>
-  <si>
-    <t>35471</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de inventário de embalagens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia! Gostaria de solicitar uma melhoria no nosso sistema de inventário de embalagens. Atualmente, ele permite apenas a contagem, sem realizar ajustes de saldo. Precisamos que, após a conclusão da contagem, seja possível finalizar o inventário com a geração automática dos ajustes necessários nos </t>
-  </si>
-  <si>
-    <t>33436</t>
-  </si>
-  <si>
-    <t>Erro de carregamento</t>
-  </si>
-  <si>
-    <t>36035</t>
-  </si>
-  <si>
-    <t>Sistema desmoldagem</t>
-  </si>
-  <si>
-    <t>10977158397</t>
-  </si>
-  <si>
-    <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM (copy)</t>
-  </si>
-  <si>
-    <t>36171</t>
-  </si>
-  <si>
-    <t>Alteração CPC para calculo de Reconhecimento de Receita</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Automação da lista de presença - Detalhar escopo</t>
-  </si>
-  <si>
-    <t>35749</t>
-  </si>
-  <si>
-    <t>Inclusão de filtro por item/peça no modulo de custos de manutenção</t>
-  </si>
-  <si>
-    <t>36078</t>
-  </si>
-  <si>
-    <t>VERIFICAÇÃO COLUNA IROG</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>36058</t>
-  </si>
-  <si>
-    <t>Apontamento de Panelas</t>
-  </si>
-  <si>
-    <t>36177</t>
-  </si>
-  <si>
-    <t>Melhorias apontamento eletrônico: Manipuladores</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos, o apontamento dos Manipuladores só precisa de mais duas coisas para tirar o papel de vez. Preciso que seja feito as seguintes alterações: - Inserir a porcentagem feita da peça no painel de produção; - Tornar as informações das paradas exclusivas do painel de paradas, trocar as aba</t>
-  </si>
-  <si>
-    <t>Maria Eduarda Santos</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>36194</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>Análise</t>
-  </si>
-  <si>
-    <t>CNPJ Alfanumérico - Instrução Normativa 2.229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De: Alexandro Fernandes Correa Enviada em: terça-feira, 20 de janeiro de 2026 07:29 Para: José Carlos Emygdio ; Rubia Maiara Raasch Mota Cc: Edson João Hammermeister Assunto: ENC: [Comunicado] CNPJ Alfanumérico - Instrução Normativa 2.229 Prioridade: Alta Bom dia Para atentarmos aos nossos sistemas </t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>36179</t>
-  </si>
-  <si>
-    <t>Erro no cálculo: Jato Dirigido</t>
-  </si>
-  <si>
-    <t>26937</t>
-  </si>
-  <si>
-    <t>BI Ronda - necessidade de implementação</t>
-  </si>
-  <si>
-    <t>35518</t>
-  </si>
-  <si>
-    <t>TEMPOS PADRÕES DE ACABAMENTO</t>
-  </si>
-  <si>
-    <t>36029</t>
-  </si>
-  <si>
-    <t>ERRO: Sistema de Custeio - Fundição</t>
-  </si>
-  <si>
-    <t>34157</t>
-  </si>
-  <si>
-    <t>Aplicação de Solda</t>
-  </si>
-  <si>
-    <t>35747</t>
+    <t>11093862537</t>
+  </si>
+  <si>
+    <t>Sequências AOD</t>
+  </si>
+  <si>
+    <t>10976998427</t>
+  </si>
+  <si>
+    <t>indicador de aderência</t>
+  </si>
+  <si>
+    <t>10977177306</t>
+  </si>
+  <si>
+    <t>Sequencia de Pre Produtivo</t>
+  </si>
+  <si>
+    <t>10976995419</t>
+  </si>
+  <si>
+    <t>Conversão KB Manutencao</t>
+  </si>
+  <si>
+    <t>11093867482</t>
+  </si>
+  <si>
+    <t>Ajustes / melhorias no sistema geração de FTF e oferta</t>
+  </si>
+  <si>
+    <t>11093916416</t>
+  </si>
+  <si>
+    <t>Verificar tickets engenharia</t>
+  </si>
+  <si>
+    <t>11141915015</t>
+  </si>
+  <si>
+    <t>Controle de pátio - Anexar NF do fornecedor</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>11093923151</t>
+  </si>
+  <si>
+    <t>Baixa Produção Cativa 9950 com data do dia 31-12-2025 (já realizado)</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>10977103624</t>
+  </si>
+  <si>
+    <t>Sistema de reconhecimento e conferência</t>
+  </si>
+  <si>
+    <t>11093921757</t>
+  </si>
+  <si>
+    <t>Alteração Peça Destruição - 166KO</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>11112488360</t>
+  </si>
+  <si>
+    <t>Estoque Consignado Binaar</t>
+  </si>
+  <si>
+    <t>11021211784</t>
+  </si>
+  <si>
+    <t>CONSULTA DE SEQ DE PRÉ-PRODUTIVO NO SISTEMA</t>
+  </si>
+  <si>
+    <t>33980</t>
+  </si>
+  <si>
+    <t>Dúvida</t>
+  </si>
+  <si>
+    <t>Qlik - Store e QVD do Comparativo de Carteira e Estoque - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Felipe, Gerar um QVD e Store dos arquivos da pasta F:\01-COMPARATIVO_CARTEIRA_DEPOSITO (as 03 abas). Cada arquivo deve ser amarrado pela "data de geração" dele.</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>23773</t>
   </si>
   <si>
     <t>Problema</t>
   </si>
   <si>
-    <t>Criar novo código de operação para o QlikSense</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos. Atualmente nós apontamos os dados da máquina Lianco (setor 1531) e Dalca (setor 1530) no sistema de Apontamento de Produção, e no QlikSense mostra exatamente os dados que apontamos, e como não apontamos uma "operação" acaba que no QlikSense não aparece código de operação. Porém is</t>
-  </si>
-  <si>
-    <t>35702</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO SISTEMA MAPEAMENTO DIGITAL</t>
-  </si>
-  <si>
-    <t>36168</t>
-  </si>
-  <si>
-    <t>SISTREMA TRANSFERENCIA BOOKING - INVOICE</t>
-  </si>
-  <si>
-    <t>36145</t>
-  </si>
-  <si>
-    <t>Consulta ligas &amp; grupos de ligas</t>
-  </si>
-  <si>
-    <t>35555</t>
-  </si>
-  <si>
-    <t>Painel Desmoldagem USE</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito algumas alterações no painel de desmoldagem USE: * Tela fica piscando, acredito que esteja atualizando a todo segundo, por favor alterar para atualizar a cada 2 minutos. (Vídeo 1) * Criar um campo de "Endereço" (Figura 1), neste campo será informado o local em que a caixa está de</t>
-  </si>
-  <si>
-    <t>Lucas da Silva Machado</t>
-  </si>
-  <si>
-    <t>33271</t>
-  </si>
-  <si>
-    <t>Alinhamento dos cálculos de disponibilidade</t>
-  </si>
-  <si>
-    <t>36165</t>
-  </si>
-  <si>
-    <t>Contabilidade</t>
-  </si>
-  <si>
-    <t>Incluir Coluna Fases no Sistema de Investimentos</t>
-  </si>
-  <si>
-    <t>Bom dia Edson, Consegues incluir no fluxo de caixa analitico uma coluna com o nome da fase do projeto. Na proxima semana temos reunião e preciamos desta informação até dia 26/01... Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Rafael Pereira</t>
-  </si>
-  <si>
-    <t>35731</t>
-  </si>
-  <si>
-    <t>Indicadores Moldes Moldagem USE</t>
-  </si>
-  <si>
-    <t>Bom dia. Preciso criar/adaptar um aplicativo do QlikSense. Hoje há um aplicativo que mostra as movimentações por sequência de peça, porém preciso que esse indicador seja apresentado por quantidade de moldes. Para isso, há a informação do sistema da quantidade de peças por placa de moldagem, conforme</t>
-  </si>
-  <si>
-    <t>27561</t>
-  </si>
-  <si>
-    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
-  </si>
-  <si>
-    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
-  </si>
-  <si>
-    <t>Guilherme Mendes</t>
-  </si>
-  <si>
-    <t>35738</t>
-  </si>
-  <si>
-    <t>Melhoria apontamento de corte de canais</t>
-  </si>
-  <si>
-    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
-  </si>
-  <si>
-    <t>36158</t>
-  </si>
-  <si>
-    <t>PROCEDIMENTOS 540 E 601</t>
-  </si>
-  <si>
-    <t>35999</t>
-  </si>
-  <si>
-    <t>Divergência no Relatório Funil Vendas 80%</t>
-  </si>
-  <si>
-    <t>Boa tarde Edson, Feliz Ano Novo!!! Conforme verificado, o processo 94/24 foi incluído no indicador de 80% em 09/01/2026, por volta das 14h30, conforme evidenciado no print abaixo. No entanto, ao gerar o relatório "Funil Vendas 80%", o processo não está sendo apresentado. Aparentemente, o relatório s</t>
-  </si>
-  <si>
-    <t>32022</t>
-  </si>
-  <si>
-    <t>Dalca e lianco - Novos Tipos no apontamento</t>
-  </si>
-  <si>
-    <t>Boa tarde! Abrindo chamado referente ao desenvolvimento do sistema de apontamentos via CLP das células de rebarbação automatizadas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Leonardo Barbosa de Moraes</t>
-  </si>
-  <si>
-    <t>13/01/2026</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>32149</t>
-  </si>
-  <si>
-    <t>ACRESENTAR BOTÃO PARA RELATORIO DE ALTERAÇÕES DE APONTMAENTOS ELETRONICOS</t>
-  </si>
-  <si>
-    <t>35047</t>
-  </si>
-  <si>
-    <t>Atualização de aplicações</t>
-  </si>
-  <si>
-    <t>36049</t>
-  </si>
-  <si>
-    <t>FLUXO ACVO - SEGURANÇA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>35081</t>
-  </si>
-  <si>
-    <t>SUGESTÃO PARA MELHORIA NA H5000</t>
-  </si>
-  <si>
-    <t>Em Análise</t>
-  </si>
-  <si>
-    <t>34347</t>
-  </si>
-  <si>
-    <t>Atualizar os Pesos 2019, 2020 e 2021 Produção das Linhas</t>
-  </si>
-  <si>
-    <t>34326</t>
-  </si>
-  <si>
-    <t>módulo custos de manutenção</t>
-  </si>
-  <si>
-    <t>34960</t>
-  </si>
-  <si>
-    <t>Correção | Status da Parcela de Pgto de Invoice</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Valorização de modelos</t>
-  </si>
-  <si>
-    <t>36012</t>
-  </si>
-  <si>
-    <t>Apontamentos de Horas Acabamento</t>
-  </si>
-  <si>
-    <t>36141</t>
-  </si>
-  <si>
-    <t>Estratificação métodos preventiva e inspeção maquinas A e B</t>
-  </si>
-  <si>
-    <t>34919</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Solicitação de BI QlikSense – Indicadores de Ofertas</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de desenvolver um BI que apresente dois indicadores relacionados ao envio de ofertas: 1. % de ofertas enviadas dentro do prazo definido no momento da abertura do PO. Este será o indicador principal. 1. Prazo médio de envio das ofertas (em dias) Apenas para acompanhamento; não haver</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>35067</t>
-  </si>
-  <si>
-    <t>Erro IROG acabamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
-  </si>
-  <si>
-    <t>Carlos Correia</t>
-  </si>
-  <si>
-    <t>36157</t>
-  </si>
-  <si>
-    <t>Acrescentar opção de apontamento de % nas linhas UPR</t>
-  </si>
-  <si>
-    <t>Acrescentar opção de apontamento de % nas linhas UPR, disponibilizar lista de 10 em 10%. A soma não pode ultrapassar os 100%.</t>
-  </si>
-  <si>
-    <t>35477</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – Gestão de Embalagens (copy)</t>
-  </si>
-  <si>
-    <t>34651</t>
-  </si>
-  <si>
-    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
-  </si>
-  <si>
-    <t>33331</t>
-  </si>
-  <si>
-    <t>[APS] - Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
-  </si>
-  <si>
-    <t>36125</t>
-  </si>
-  <si>
-    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
-  </si>
-  <si>
-    <t>36106</t>
-  </si>
-  <si>
-    <t>Sequências AOD</t>
-  </si>
-  <si>
-    <t>35500</t>
-  </si>
-  <si>
-    <t>indicador de aderência</t>
-  </si>
-  <si>
-    <t>33651</t>
-  </si>
-  <si>
-    <t>Sequencia de Pre Produtivo</t>
-  </si>
-  <si>
-    <t>10976995419</t>
-  </si>
-  <si>
-    <t>Conversão KB Manutencao</t>
-  </si>
-  <si>
-    <t>36120</t>
-  </si>
-  <si>
-    <t>Ajustes / melhorias no sistema geração de FTF e oferta</t>
-  </si>
-  <si>
-    <t>36006</t>
-  </si>
-  <si>
-    <t>Verificar tickets engenharia</t>
-  </si>
-  <si>
-    <t>Controle de pátio - Anexar NF do fornecedor</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>35988</t>
-  </si>
-  <si>
-    <t>Baixa Produção Cativa 9950 com data do dia 31-12-2025 (já realizado)</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Sistema de reconhecimento e conferência</t>
-  </si>
-  <si>
-    <t>35993</t>
-  </si>
-  <si>
-    <t>Alteração Peça Destruição - 166KO</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>36278</t>
-  </si>
-  <si>
-    <t>Estoque Consignado Binaar</t>
-  </si>
-  <si>
-    <t>31398</t>
-  </si>
-  <si>
-    <t>CONSULTA DE SEQ DE PRÉ-PRODUTIVO NO SISTEMA</t>
-  </si>
-  <si>
-    <t>33980</t>
-  </si>
-  <si>
-    <t>Dúvida</t>
-  </si>
-  <si>
-    <t>Qlik - Store e QVD do Comparativo de Carteira e Estoque - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Felipe, Gerar um QVD e Store dos arquivos da pasta F:\01-COMPARATIVO_CARTEIRA_DEPOSITO (as 03 abas). Cada arquivo deve ser amarrado pela "data de geração" dele.</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>23773</t>
-  </si>
-  <si>
     <t>Registro de moldagem USE/ULE</t>
   </si>
   <si>
@@ -1140,18 +1125,12 @@
     <t>22/04/2026</t>
   </si>
   <si>
-    <t>35378</t>
+    <t>11021632671</t>
   </si>
   <si>
     <t>Qliksense - Aplicação Refugo</t>
   </si>
   <si>
-    <t>Bom dia, Gostaria que fosse inserido o motivo do refugo na quarta aba, na tabela abaixo: Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Raiana Correa</t>
-  </si>
-  <si>
     <t>36218</t>
   </si>
   <si>
@@ -1170,18 +1149,12 @@
     <t>22/01/2026</t>
   </si>
   <si>
-    <t>34986</t>
+    <t>11021290917</t>
   </si>
   <si>
     <t>Registro de inspeção</t>
   </si>
   <si>
-    <t>Bom dia! Favor verificar o setor 7997- reteste USE, pois quando é feita a movimentação o mesmo está puxando o registro de Partícula Magnética onde o mesmo deve registrar somente " Reteste " pois a sequência abaixo é uma peça de aço inoxidável e é realizado somente o ensaio de Liquido penetrante. Obr</t>
-  </si>
-  <si>
-    <t>Mauro Morais</t>
-  </si>
-  <si>
     <t>29848</t>
   </si>
   <si>
@@ -1212,7 +1185,7 @@
     <t xml:space="preserve">Bom dia Felipe. Movimentação das sequências a seguir não estão aparecendo na aplicação. Seq. Modelo Cód. Cliente Cliente Grupo de Cliente Sub-U.N. U.N. Liga Grupo liga Quantidade Peso BR Unit Peso Total Dias no Setor Setor Descrição do setor Data fusão Data Recebida 040LS IC58C3200580 26004 KOMATSU </t>
   </si>
   <si>
-    <t>27250</t>
+    <t>11021311326</t>
   </si>
   <si>
     <t>Problemas APP de Moldagem</t>
@@ -1227,16 +1200,19 @@
     <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
   </si>
   <si>
+    <t>11141837000</t>
+  </si>
+  <si>
     <t>Controle de pátio - Recebimento</t>
   </si>
   <si>
-    <t>35483</t>
+    <t>11133939050</t>
   </si>
   <si>
     <t>Unidade de medida nos métodos</t>
   </si>
   <si>
-    <t>29/01/2026</t>
+    <t>11235596537</t>
   </si>
   <si>
     <t>10/02/2026</t>
@@ -1251,7 +1227,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2026-06</t>
+    <t>Ago/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1878,7 +1854,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1887,30 +1863,30 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1922,10 +1898,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1934,7 +1910,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1942,37 +1918,37 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1981,45 +1957,45 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -2036,7 +2012,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -2048,10 +2024,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -2066,7 +2042,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -2083,43 +2059,43 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -2130,25 +2106,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -2160,13 +2136,13 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -2177,7 +2153,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -2189,10 +2165,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -2204,10 +2180,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -2216,7 +2192,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -2224,37 +2200,37 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -2266,48 +2242,48 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -2318,46 +2294,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="M13" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -2365,7 +2341,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -2374,37 +2350,37 @@
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2412,43 +2388,43 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -2459,7 +2435,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -2471,10 +2447,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -2486,10 +2462,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -2498,7 +2474,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2506,22 +2482,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2533,10 +2509,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2545,7 +2521,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2553,46 +2529,46 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2600,46 +2576,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M19" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2647,22 +2623,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2674,10 +2650,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2686,7 +2662,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2694,46 +2670,46 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2741,7 +2717,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2753,13 +2729,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
@@ -2768,57 +2744,57 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2835,7 +2811,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2847,10 +2823,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2862,10 +2838,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2874,7 +2850,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2882,46 +2858,46 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2929,7 +2905,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2941,10 +2917,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2956,10 +2932,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2968,7 +2944,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2976,46 +2952,46 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -3023,7 +2999,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -3035,10 +3011,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -3053,13 +3029,13 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>27</v>
@@ -3070,7 +3046,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -3082,10 +3058,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -3100,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -3117,7 +3093,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -3129,10 +3105,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -3147,13 +3123,13 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -3164,37 +3140,37 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -3211,7 +3187,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -3223,10 +3199,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -3238,19 +3214,19 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -3258,7 +3234,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -3270,10 +3246,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -3288,13 +3264,13 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -3305,7 +3281,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -3317,10 +3293,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -3332,19 +3308,19 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -3352,37 +3328,37 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -3391,7 +3367,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -3399,7 +3375,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -3411,10 +3387,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -3426,10 +3402,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -3438,7 +3414,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -3446,7 +3422,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3458,13 +3434,13 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>21</v>
@@ -3476,13 +3452,13 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -3493,43 +3469,43 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -3540,43 +3516,43 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
@@ -3587,43 +3563,43 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -3634,43 +3610,43 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>27</v>
@@ -3681,7 +3657,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3693,10 +3669,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3711,13 +3687,13 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -3728,7 +3704,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3740,10 +3716,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3755,10 +3731,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3767,7 +3743,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -3775,22 +3751,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3802,10 +3778,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3814,7 +3790,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3822,7 +3798,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3834,10 +3810,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3852,7 +3828,7 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3869,43 +3845,43 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>27</v>
@@ -3916,25 +3892,25 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
@@ -3946,7 +3922,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3963,37 +3939,37 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -4002,7 +3978,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -4010,7 +3986,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -4022,10 +3998,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -4037,10 +4013,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -4049,7 +4025,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -4057,7 +4033,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -4066,34 +4042,34 @@
         <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
@@ -4104,37 +4080,37 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -4151,22 +4127,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -4178,10 +4154,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -4190,7 +4166,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -4198,7 +4174,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -4210,10 +4186,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -4225,19 +4201,19 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -4245,7 +4221,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -4257,10 +4233,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -4275,13 +4251,13 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
@@ -4292,7 +4268,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -4304,10 +4280,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -4319,19 +4295,19 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -4339,7 +4315,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -4351,10 +4327,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -4369,7 +4345,7 @@
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -4386,7 +4362,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -4398,13 +4374,13 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>21</v>
@@ -4416,7 +4392,7 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -4433,7 +4409,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -4445,10 +4421,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -4460,10 +4436,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -4472,7 +4448,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -4480,43 +4456,43 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>27</v>
@@ -4527,7 +4503,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4539,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4554,10 +4530,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4566,7 +4542,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -4574,46 +4550,46 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -4621,37 +4597,37 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4660,7 +4636,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -4668,22 +4644,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4695,19 +4671,19 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -4715,7 +4691,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4727,13 +4703,13 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>21</v>
@@ -4745,13 +4721,13 @@
         <v>23</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>27</v>
@@ -4762,7 +4738,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4774,10 +4750,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4792,13 +4768,13 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>27</v>
@@ -4809,7 +4785,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4821,10 +4797,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4836,10 +4812,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4848,7 +4824,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>
@@ -4856,22 +4832,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4883,10 +4859,10 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4895,7 +4871,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -4903,7 +4879,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4912,34 +4888,34 @@
         <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>27</v>
@@ -4950,7 +4926,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4962,10 +4938,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4980,7 +4956,7 @@
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4997,7 +4973,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -5009,10 +4985,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -5024,19 +5000,19 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>28</v>
@@ -5044,7 +5020,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -5056,10 +5032,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -5071,10 +5047,10 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -5083,7 +5059,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>28</v>
@@ -5091,7 +5067,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -5100,28 +5076,28 @@
         <v>17</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -5168,13 +5144,13 @@
         <v>23</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>27</v>
@@ -5188,43 +5164,43 @@
         <v>259</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>28</v>
@@ -5232,43 +5208,43 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E75" s="2" t="s">
+      <c r="G75" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="I75" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>27</v>
@@ -5279,46 +5255,46 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="L76" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
@@ -5326,43 +5302,43 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>27</v>
@@ -5373,7 +5349,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -5385,10 +5361,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -5400,10 +5376,10 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -5412,7 +5388,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>28</v>
@@ -5420,46 +5396,46 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="I79" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J79" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K79" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M79" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>28</v>
@@ -5476,28 +5452,28 @@
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>280</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>283</v>
+        <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>284</v>
+        <v>68</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -5514,22 +5490,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5541,10 +5517,10 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5553,7 +5529,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>28</v>
@@ -5561,7 +5537,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5573,10 +5549,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5588,19 +5564,19 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>28</v>
@@ -5608,7 +5584,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5620,10 +5596,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5635,10 +5611,10 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5647,7 +5623,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>28</v>
@@ -5655,7 +5631,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5667,10 +5643,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5685,13 +5661,13 @@
         <v>23</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>27</v>
@@ -5702,22 +5678,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5729,10 +5705,10 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -5741,7 +5717,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>28</v>
@@ -5749,22 +5725,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5776,10 +5752,10 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5788,7 +5764,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>28</v>
@@ -5796,46 +5772,46 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>28</v>
@@ -5843,25 +5819,25 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>21</v>
@@ -5870,19 +5846,19 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="L88" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M88" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>28</v>
@@ -5890,7 +5866,7 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5902,10 +5878,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5917,19 +5893,19 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>28</v>
@@ -5937,7 +5913,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5949,10 +5925,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5964,10 +5940,10 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>25</v>
@@ -5976,7 +5952,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O90" s="2" t="s">
         <v>28</v>
@@ -5984,43 +5960,43 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="I91" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>27</v>
@@ -6031,22 +6007,22 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -6058,19 +6034,19 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>28</v>
@@ -6078,43 +6054,43 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>27</v>
@@ -6125,46 +6101,46 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O94" s="2" t="s">
         <v>28</v>
@@ -6172,7 +6148,7 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -6184,10 +6160,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -6202,13 +6178,13 @@
         <v>23</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -6219,7 +6195,7 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
@@ -6231,10 +6207,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -6249,13 +6225,13 @@
         <v>23</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>27</v>
@@ -6266,7 +6242,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
@@ -6278,10 +6254,10 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -6296,13 +6272,13 @@
         <v>23</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>27</v>
@@ -6313,46 +6289,46 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>96</v>
+        <v>323</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O98" s="2" t="s">
         <v>28</v>
@@ -6360,7 +6336,7 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>16</v>
@@ -6372,10 +6348,10 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
@@ -6387,10 +6363,10 @@
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>25</v>
@@ -6399,7 +6375,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>28</v>
@@ -6407,7 +6383,7 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>16</v>
@@ -6419,10 +6395,10 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>20</v>
@@ -6437,13 +6413,13 @@
         <v>23</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>27</v>
@@ -6454,7 +6430,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>16</v>
@@ -6466,10 +6442,10 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
@@ -6484,13 +6460,13 @@
         <v>23</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>27</v>
@@ -6501,7 +6477,7 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>16</v>
@@ -6513,10 +6489,10 @@
         <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>20</v>
@@ -6531,13 +6507,13 @@
         <v>23</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>27</v>
@@ -6548,7 +6524,7 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>16</v>
@@ -6560,10 +6536,10 @@
         <v>18</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>20</v>
@@ -6575,19 +6551,19 @@
         <v>22</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O103" s="2" t="s">
         <v>28</v>
@@ -6595,22 +6571,22 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>20</v>
@@ -6622,19 +6598,19 @@
         <v>22</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O104" s="2" t="s">
         <v>28</v>
@@ -6642,22 +6618,22 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>29</v>
+        <v>336</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>20</v>
@@ -6669,10 +6645,10 @@
         <v>22</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>25</v>
@@ -6681,7 +6657,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="O105" s="2" t="s">
         <v>28</v>
@@ -6689,7 +6665,7 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>16</v>
@@ -6701,10 +6677,10 @@
         <v>18</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>20</v>
@@ -6716,10 +6692,10 @@
         <v>22</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>25</v>
@@ -6728,7 +6704,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>28</v>
@@ -6736,54 +6712,54 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O107" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M107" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N107" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>16</v>
@@ -6795,10 +6771,10 @@
         <v>18</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>20</v>
@@ -6813,13 +6789,13 @@
         <v>23</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>27</v>
@@ -6830,7 +6806,7 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>16</v>
@@ -6842,10 +6818,10 @@
         <v>18</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>20</v>
@@ -6857,10 +6833,10 @@
         <v>22</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>25</v>
@@ -6869,7 +6845,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O109" s="2" t="s">
         <v>28</v>
@@ -6877,46 +6853,46 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C110" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L110" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="M110" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O110" s="2" t="s">
         <v>28</v>
@@ -6924,7 +6900,7 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>16</v>
@@ -6936,13 +6912,13 @@
         <v>18</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>21</v>
@@ -6951,10 +6927,10 @@
         <v>22</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>25</v>
@@ -6963,7 +6939,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O111" s="2" t="s">
         <v>28</v>
@@ -6971,22 +6947,22 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>20</v>
@@ -6998,10 +6974,10 @@
         <v>22</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>25</v>
@@ -7010,7 +6986,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>28</v>
@@ -7018,84 +6994,84 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O113" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M113" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N113" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>244</v>
+        <v>365</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>25</v>
@@ -7104,7 +7080,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O114" s="2" t="s">
         <v>28</v>
@@ -7112,7 +7088,7 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>16</v>
@@ -7121,37 +7097,37 @@
         <v>17</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O115" s="2" t="s">
         <v>28</v>
@@ -7159,46 +7135,46 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O116" s="2" t="s">
         <v>28</v>
@@ -7206,25 +7182,25 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>21</v>
@@ -7233,19 +7209,19 @@
         <v>22</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>24</v>
+        <v>268</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O117" s="2" t="s">
         <v>28</v>
@@ -7253,46 +7229,46 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>28</v>
@@ -7300,46 +7276,46 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>28</v>
@@ -7347,46 +7323,46 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>28</v>
@@ -7394,37 +7370,37 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>244</v>
+        <v>365</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>25</v>
@@ -7433,7 +7409,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>28</v>
@@ -7441,22 +7417,22 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>20</v>
@@ -7468,19 +7444,19 @@
         <v>22</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>28</v>
@@ -7488,46 +7464,46 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O123" s="2" t="s">
         <v>28</v>
@@ -7535,46 +7511,46 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L124" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="M124" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>28</v>
@@ -7582,7 +7558,7 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>16</v>
@@ -7594,10 +7570,10 @@
         <v>18</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>20</v>
@@ -7609,10 +7585,10 @@
         <v>22</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>407</v>
+        <v>244</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>24</v>
+        <v>268</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>25</v>
@@ -7621,7 +7597,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>28</v>
@@ -7629,22 +7605,22 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>29</v>
+        <v>399</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>20</v>
@@ -7656,10 +7632,10 @@
         <v>22</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="L126" s="2" t="s">
         <v>25</v>
@@ -7671,7 +7647,7 @@
         <v>27</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -7687,23 +7663,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7711,16 +7687,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7731,15 +7707,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>76.6</v>
+        <v>26.36</v>
       </c>
       <c r="J5" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -7752,7 +7728,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -7760,7 +7736,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7791,12 +7767,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B2">
         <v>125</v>
@@ -7810,35 +7786,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>76.6</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7846,7 +7822,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -7855,13 +7831,13 @@
         <v>92</v>
       </c>
       <c r="G10" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7873,27 +7849,27 @@
         <v>52</v>
       </c>
       <c r="P10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H11">
         <v>17</v>
@@ -7902,10 +7878,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="M11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11">
         <v>52</v>
@@ -7914,18 +7890,18 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -7937,62 +7913,62 @@
         <v>103</v>
       </c>
       <c r="J12" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="K12">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N12">
         <v>7</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q12">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H13">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N13">
         <v>2</v>
       </c>
       <c r="P13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q13">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>30</v>
@@ -8001,33 +7977,33 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -8035,13 +8011,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -8049,24 +8025,44 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -8074,150 +8070,156 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F21" s="2">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>389</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>97</v>
+        <v>282</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>390</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>370</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2">
+        <v>282</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>298</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="F24" s="2">
-        <v>70</v>
+        <v>282</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>299</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>396</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>70</v>
+        <v>282</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>397</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>65</v>
+        <v>282</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="F27" s="2">
-        <v>65</v>
+        <v>282</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>199</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F28" s="2">
-        <v>53</v>
+        <v>282</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F29" s="2">
-        <v>53</v>
+        <v>282</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>279</v>
+        <v>120</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>41</v>
+        <v>282</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>280</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
